--- a/backend/chunking/ChromaDB_Export.xlsx
+++ b/backend/chunking/ChromaDB_Export.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Khoa_Luan\Source_code\backend\chunking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FDBF823-E72F-4BAB-BE4E-A6774BECD946}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F068352D-29D2-45BE-92E5-357120FB7599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2385,7 +2385,7 @@
   <cols>
     <col min="1" max="1" width="48.6640625" customWidth="1"/>
     <col min="2" max="2" width="146.44140625" customWidth="1"/>
-    <col min="3" max="3" width="33.77734375" customWidth="1"/>
+    <col min="3" max="3" width="42.77734375" customWidth="1"/>
     <col min="4" max="4" width="19.33203125" customWidth="1"/>
   </cols>
   <sheetData>
